--- a/DateBase/orders/Dang Nguyen48_2026-6-24.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-24.xlsx
@@ -523,6 +523,9 @@
       <c r="C11" t="str">
         <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -581,7 +584,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>09515812103850</v>
+        <v>09515812103858</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-24.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -527,9 +527,86 @@
         <v>8</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F18" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>859_喷色小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>875_九星叶红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -584,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>09515812103858</v>
+        <v>0951581210385855552512550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-24.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-24.xlsx
@@ -603,6 +603,9 @@
       <c r="C21" t="str">
         <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
       </c>
+      <c r="F21" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0951581210385855552512550</v>
+        <v>0951581210385855552512551</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-24.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -604,12 +604,90 @@
         <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
       </c>
       <c r="F21" t="str">
-        <v>1</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>118_绣球老绿_Hydrangea Garden Lace_Hydrangea L._1stem</v>
+      </c>
+      <c r="F22" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>4</v>
+      </c>
+      <c r="C23" t="str">
+        <v>118_绣球老绿_Hydrangea Garden Lace_Hydrangea L._1stem</v>
+      </c>
+      <c r="F23" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F25" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>85_摩洛哥_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>5</v>
+      </c>
+      <c r="C30" t="str">
+        <v>855_海芋粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L30"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +742,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0951581210385855552512551</v>
+        <v>0951581210385855552512551515261520512563</v>
       </c>
     </row>
   </sheetData>
